--- a/history_matching/example/Params.xlsx
+++ b/history_matching/example/Params.xlsx
@@ -436,10 +436,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>-5</v>
+        <v>-50</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -447,10 +447,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>7.2</v>
+        <v>-100</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>25.9</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
